--- a/Ciclo 01/MOP/Plantilla_Solver_Pizzeria_M_y_M.xlsx
+++ b/Ciclo 01/MOP/Plantilla_Solver_Pizzeria_M_y_M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 01\MOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B25DC30-2008-4750-B12B-9E531AD86B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E8A538-62FF-42E8-9F75-1DD0B65A3553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informe de respuestas 3" sheetId="9" r:id="rId1"/>
@@ -474,7 +474,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.##"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,14 +553,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="18"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -688,7 +680,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -750,55 +742,38 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1100,8 +1075,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
+    <row r="6" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
       <c r="B6" s="23" t="s">
         <v>35</v>
       </c>
@@ -1112,8 +1087,8 @@
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
     </row>
-    <row r="7" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
+    <row r="7" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="35"/>
       <c r="B7" s="23" t="s">
         <v>99</v>
       </c>
@@ -1124,8 +1099,8 @@
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
     </row>
-    <row r="8" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
+    <row r="8" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
       <c r="B8" s="23" t="s">
         <v>100</v>
       </c>
@@ -1136,8 +1111,8 @@
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+    <row r="9" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="23"/>
@@ -1148,7 +1123,7 @@
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="23" t="s">
         <v>37</v>
@@ -1160,7 +1135,7 @@
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
     </row>
-    <row r="11" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23"/>
       <c r="B11" s="23" t="s">
         <v>38</v>
@@ -1172,7 +1147,7 @@
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -1206,16 +1181,16 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23"/>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="36" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="23"/>
@@ -1224,16 +1199,16 @@
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23"/>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="37">
         <v>268</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="37">
         <v>268</v>
       </c>
       <c r="F16" s="23"/>
@@ -1274,19 +1249,19 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="23"/>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="36" t="s">
         <v>45</v>
       </c>
       <c r="G20" s="23"/>
@@ -1294,31 +1269,31 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
     </row>
     <row r="22" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23"/>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="33">
         <v>10</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="33">
         <v>10</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="33" t="s">
         <v>54</v>
       </c>
       <c r="G22" s="23"/>
@@ -1326,19 +1301,19 @@
     </row>
     <row r="23" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A23" s="23"/>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="46">
+      <c r="D23" s="33">
         <v>45</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="33">
         <v>45</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="33" t="s">
         <v>54</v>
       </c>
       <c r="G23" s="23"/>
@@ -1346,19 +1321,19 @@
     </row>
     <row r="24" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A24" s="23"/>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="33">
         <v>10</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="33">
         <v>10</v>
       </c>
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="33" t="s">
         <v>54</v>
       </c>
       <c r="G24" s="23"/>
@@ -1366,19 +1341,19 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="23"/>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="47">
+      <c r="D25" s="34">
         <v>50</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="34">
         <v>50</v>
       </c>
-      <c r="F25" s="41" t="s">
+      <c r="F25" s="34" t="s">
         <v>54</v>
       </c>
       <c r="G25" s="23"/>
@@ -1386,11 +1361,11 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="23"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="42"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
     </row>
@@ -1428,374 +1403,374 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="44" t="s">
+      <c r="B30" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="44" t="s">
+      <c r="G30" s="36" t="s">
         <v>49</v>
       </c>
       <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="23"/>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="23"/>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="38">
         <v>105</v>
       </c>
-      <c r="E32" s="40" t="s">
+      <c r="E32" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="40" t="s">
+      <c r="F32" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G32" s="40">
+      <c r="G32" s="33">
         <v>5</v>
       </c>
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="23"/>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D33" s="49">
+      <c r="D33" s="38">
         <v>60</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="40" t="s">
+      <c r="F33" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G33" s="40">
+      <c r="G33" s="33">
         <v>0</v>
       </c>
       <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23"/>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="49">
+      <c r="D34" s="38">
         <v>0</v>
       </c>
-      <c r="E34" s="40" t="s">
+      <c r="E34" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="40" t="s">
+      <c r="F34" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G34" s="40">
+      <c r="G34" s="33">
         <v>0</v>
       </c>
       <c r="H34" s="23"/>
     </row>
     <row r="35" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A35" s="23"/>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="40" t="s">
+      <c r="C35" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D35" s="49">
+      <c r="D35" s="38">
         <v>0</v>
       </c>
-      <c r="E35" s="40" t="s">
+      <c r="E35" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="40">
+      <c r="G35" s="33">
         <v>0</v>
       </c>
       <c r="H35" s="23"/>
     </row>
     <row r="36" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="40" t="s">
+      <c r="C36" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="49">
+      <c r="D36" s="38">
         <v>16.25</v>
       </c>
-      <c r="E36" s="40" t="s">
+      <c r="E36" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F36" s="40" t="s">
+      <c r="F36" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="33">
         <v>3.75</v>
       </c>
       <c r="H36" s="23"/>
     </row>
     <row r="37" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A37" s="23"/>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="49">
+      <c r="D37" s="38">
         <v>27.75</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="40">
+      <c r="G37" s="33">
         <v>0.25</v>
       </c>
       <c r="H37" s="23"/>
     </row>
     <row r="38" spans="1:8" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="40" t="s">
+      <c r="C38" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="49">
+      <c r="D38" s="38">
         <v>680</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="33">
         <v>120</v>
       </c>
       <c r="H38" s="23"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="23"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="49"/>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
       <c r="H39" s="23"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="23"/>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C40" s="40" t="s">
+      <c r="C40" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D40" s="46">
+      <c r="D40" s="33">
         <v>10</v>
       </c>
-      <c r="E40" s="40" t="s">
+      <c r="E40" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="40" t="s">
+      <c r="F40" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="40">
+      <c r="G40" s="33">
         <v>15</v>
       </c>
       <c r="H40" s="23"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="23"/>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="46">
+      <c r="D41" s="33">
         <v>10</v>
       </c>
-      <c r="E41" s="40" t="s">
+      <c r="E41" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="F41" s="40" t="s">
+      <c r="F41" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G41" s="46">
+      <c r="G41" s="33">
         <v>0</v>
       </c>
       <c r="H41" s="23"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="23"/>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="46">
+      <c r="D42" s="33">
         <v>45</v>
       </c>
-      <c r="E42" s="40" t="s">
+      <c r="E42" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F42" s="40" t="s">
+      <c r="F42" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="33">
         <v>0</v>
       </c>
       <c r="H42" s="23"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="23"/>
-      <c r="B43" s="40" t="s">
+      <c r="B43" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="46">
+      <c r="D43" s="33">
         <v>45</v>
       </c>
-      <c r="E43" s="40" t="s">
+      <c r="E43" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="40" t="s">
+      <c r="F43" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G43" s="46">
+      <c r="G43" s="33">
         <v>25</v>
       </c>
       <c r="H43" s="23"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="23"/>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="46">
+      <c r="D44" s="33">
         <v>10</v>
       </c>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="40" t="s">
+      <c r="F44" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G44" s="40">
+      <c r="G44" s="33">
         <v>10</v>
       </c>
       <c r="H44" s="23"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="23"/>
-      <c r="B45" s="40" t="s">
+      <c r="B45" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D45" s="46">
+      <c r="D45" s="33">
         <v>10</v>
       </c>
-      <c r="E45" s="40" t="s">
+      <c r="E45" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="F45" s="40" t="s">
+      <c r="F45" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G45" s="46">
+      <c r="G45" s="33">
         <v>5</v>
       </c>
       <c r="H45" s="23"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="23"/>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="46">
+      <c r="D46" s="33">
         <v>50</v>
       </c>
-      <c r="E46" s="40" t="s">
+      <c r="E46" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="F46" s="40" t="s">
+      <c r="F46" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G46" s="40">
+      <c r="G46" s="33">
         <v>0</v>
       </c>
       <c r="H46" s="23"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="23"/>
-      <c r="B47" s="41" t="s">
+      <c r="B47" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C47" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D47" s="47">
+      <c r="D47" s="34">
         <v>50</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="E47" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F47" s="41" t="s">
+      <c r="F47" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="G47" s="47">
+      <c r="G47" s="34">
         <v>30</v>
       </c>
       <c r="H47" s="23"/>
@@ -1827,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EEDB9B9-1DAD-49A2-868C-A15AB37256AA}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1881,172 +1856,172 @@
       <c r="J6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="38" t="s">
+      <c r="H7" s="31" t="s">
         <v>86</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="32" t="s">
         <v>88</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="33">
         <v>10</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="33">
         <v>-0.25000000000000044</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="33">
         <v>5</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="33">
         <v>0.25000000000000044</v>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="33">
         <v>1E+30</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
     </row>
     <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="33">
         <v>45</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="33">
         <v>0.65000000000000036</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="33">
         <v>2.4000000000000004</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="33">
         <v>1E+30</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="33">
         <v>0.65000000000000036</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
     </row>
     <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="33">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="33">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="33">
         <v>3.5</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="33">
         <v>1.3000000000000007</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="33">
         <v>0.16666666666666696</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="34">
         <v>50</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="34">
         <v>0.625</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="34">
         <v>1.5</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="34">
         <v>1E+30</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="34">
         <v>0.625</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
     </row>
@@ -2076,205 +2051,205 @@
       <c r="J16" s="23"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38" t="s">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="38" t="s">
+      <c r="F17" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G17" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="31" t="s">
         <v>86</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
     </row>
     <row r="18" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="39" t="s">
+      <c r="H18" s="32" t="s">
         <v>88</v>
       </c>
       <c r="I18" s="23"/>
       <c r="J18" s="23"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
       <c r="I19" s="23"/>
       <c r="J19" s="23"/>
     </row>
     <row r="20" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="33">
         <v>105</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="33">
         <v>0</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="33">
         <v>110</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="33">
         <v>1E+30</v>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="33">
         <v>5.0000000000000018</v>
       </c>
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
     </row>
     <row r="21" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="33">
         <v>60</v>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="33">
         <v>3.5</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="33">
         <v>60</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="33">
         <v>0.62500000000001454</v>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="33">
         <v>5</v>
       </c>
       <c r="I21" s="23"/>
       <c r="J21" s="23"/>
     </row>
     <row r="22" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="33">
         <v>0</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="33">
         <v>0</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="33">
         <v>0</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="33">
         <v>1E+30</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="33">
         <v>0</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
     </row>
     <row r="23" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="25">
         <v>0</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="25">
         <v>0</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="25">
         <v>0</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="25">
         <v>1E+30</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="25">
         <v>16.25</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="25">
         <v>0</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="25">
         <v>20</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="25">
         <v>1E+30</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="25">
         <v>3.7499999999999982</v>
       </c>
     </row>
     <row r="25" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="25">
         <v>27.75</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="25">
         <v>0</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="25">
         <v>28</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="25">
         <v>1E+30</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="25">
         <v>0.25000000000000577</v>
       </c>
     </row>
@@ -2300,15 +2275,6 @@
       <c r="H26" s="24">
         <v>120</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2317,12 +2283,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53F17F9-528F-4F20-8952-2283E6C5C5CE}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2.28515625" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
@@ -2332,185 +2298,441 @@
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="32"/>
-      <c r="C6" s="32" t="s">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="23"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="32"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="33" t="s">
+      <c r="D6" s="31"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
+      <c r="B7" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="32" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="24" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="37">
         <v>268</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32" t="s">
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="23"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="F11" s="32" t="s">
+      <c r="D11" s="31"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="31" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="33" t="s">
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="H12" s="23"/>
+      <c r="I12" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="32" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="23"/>
+      <c r="B13" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="33">
         <v>10</v>
       </c>
-      <c r="F13" s="28">
+      <c r="E13" s="23"/>
+      <c r="F13" s="33">
         <v>10</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="33">
         <v>268</v>
       </c>
-      <c r="I13" s="28">
+      <c r="H13" s="23"/>
+      <c r="I13" s="33">
         <v>10</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="33">
         <v>268</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="23"/>
+      <c r="B14" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="33">
         <v>45</v>
       </c>
-      <c r="F14" s="28">
+      <c r="E14" s="23"/>
+      <c r="F14" s="33">
         <v>20</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="33">
         <v>208</v>
       </c>
-      <c r="I14" s="28">
+      <c r="H14" s="23"/>
+      <c r="I14" s="33">
         <v>45</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="33">
         <v>268</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="23"/>
+      <c r="B15" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="33">
         <v>10</v>
       </c>
-      <c r="F15" s="28">
+      <c r="E15" s="23"/>
+      <c r="F15" s="33">
         <v>5</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="33">
         <v>250.5</v>
       </c>
-      <c r="I15" s="28">
+      <c r="H15" s="23"/>
+      <c r="I15" s="33">
         <v>10</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="33">
         <v>268</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="34">
         <v>50</v>
       </c>
-      <c r="F16" s="29">
+      <c r="E16" s="23"/>
+      <c r="F16" s="34">
         <v>20</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="34">
         <v>223</v>
       </c>
-      <c r="I16" s="29">
+      <c r="H16" s="23"/>
+      <c r="I16" s="34">
         <v>50</v>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="34">
         <v>268</v>
       </c>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2814,15 +3036,15 @@
       </c>
     </row>
     <row r="16" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="17"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="37"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="30"/>
     </row>
     <row r="17" spans="2:10" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
